--- a/data/trans_dic/P39A4_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P39A4_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 92,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>90,95; 96,9</t>
+          <t>91,09; 96,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91,47; 95,14</t>
+          <t>91,67; 95,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92,45; 95,47</t>
+          <t>92,35; 95,57</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>91,42; 97,01</t>
+          <t>91,26; 96,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91,54; 94,43</t>
+          <t>91,63; 94,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92,1; 95,86</t>
+          <t>92,08; 96,21</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>85,73; 92,15</t>
+          <t>86,64; 92,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,87; 97,31</t>
+          <t>91,73; 97,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90,31; 95,41</t>
+          <t>90,3; 95,18</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,26; 93,9</t>
+          <t>89,94; 93,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67,27; 92,99</t>
+          <t>64,01; 92,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74,06; 92,66</t>
+          <t>76,03; 92,86</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>91,53; 94,55</t>
+          <t>91,62; 94,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>83,21; 93,75</t>
+          <t>84,46; 93,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88,25; 93,4</t>
+          <t>88,71; 93,49</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 92,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>521468; 555601</t>
+          <t>522275; 554925</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>563239; 585833</t>
+          <t>564488; 586043</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1099318; 1135322</t>
+          <t>1098173; 1136472</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1025102; 1087839</t>
+          <t>1023342; 1087161</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>820002; 845921</t>
+          <t>820849; 846290</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1857770; 1933668</t>
+          <t>1857399; 1940702</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>580608; 624128</t>
+          <t>586760; 627637</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>791329; 838178</t>
+          <t>790147; 839799</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1389598; 1468055</t>
+          <t>1389368; 1464415</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>783113; 814673</t>
+          <t>780267; 813998</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>687564; 950439</t>
+          <t>654203; 949723</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1399547; 1750959</t>
+          <t>1436790; 1754818</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2965068; 3063135</t>
+          <t>2968242; 3063766</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2824859; 3182742</t>
+          <t>2867313; 3185179</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5855033; 6196508</t>
+          <t>5885563; 6202989</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A4_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P39A4_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91,09; 96,78</t>
+          <t>93,67; 97,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91,67; 95,17</t>
+          <t>91,28; 94,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92,35; 95,57</t>
+          <t>93,09; 95,59</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>91,26; 96,95</t>
+          <t>89,97; 94,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91,63; 94,47</t>
+          <t>90,98; 93,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92,08; 96,21</t>
+          <t>91,13; 93,59</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>90,08%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86,64; 92,67</t>
+          <t>85,4; 91,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,73; 97,49</t>
+          <t>89,37; 93,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90,3; 95,18</t>
+          <t>88,24; 91,78</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,94; 93,82</t>
+          <t>89,41; 93,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,01; 92,92</t>
+          <t>90,34; 93,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,03; 92,86</t>
+          <t>90,59; 93,19</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>91,62; 94,57</t>
+          <t>90,75; 93,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>84,46; 93,82</t>
+          <t>91,47; 93,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88,71; 93,49</t>
+          <t>91,33; 92,76</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>546183</t>
+          <t>588615</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>576221</t>
+          <t>617180</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1122404</t>
+          <t>1205796</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>522275; 554925</t>
+          <t>576079; 597138</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>564488; 586043</t>
+          <t>604048; 626849</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1098173; 1136472</t>
+          <t>1188548; 1220454</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1053465</t>
+          <t>880935</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>834674</t>
+          <t>923695</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1888139</t>
+          <t>1804630</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1023342; 1087161</t>
+          <t>860099; 899014</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>820849; 846290</t>
+          <t>907279; 937272</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1857399; 1940702</t>
+          <t>1779989; 1827975</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>608852</t>
+          <t>679108</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>812375</t>
+          <t>701768</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1421227</t>
+          <t>1380876</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>586760; 627637</t>
+          <t>653730; 698502</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>790147; 839799</t>
+          <t>685803; 715471</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1389368; 1464415</t>
+          <t>1352637; 1406890</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>799755</t>
+          <t>842183</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>881795</t>
+          <t>947439</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1681550</t>
+          <t>1789622</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>780267; 813998</t>
+          <t>820806; 859174</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>654203; 949723</t>
+          <t>930497; 961849</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1436790; 1754818</t>
+          <t>1764784; 1815411</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3008256</t>
+          <t>2990841</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3105063</t>
+          <t>3190083</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6113319</t>
+          <t>6180923</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2968242; 3063766</t>
+          <t>2953393; 3027169</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2867313; 3185179</t>
+          <t>3161598; 3217929</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5885563; 6202989</t>
+          <t>6128895; 6224926</t>
         </is>
       </c>
     </row>
